--- a/缓存数据/ds_count_8_Part.xlsx
+++ b/缓存数据/ds_count_8_Part.xlsx
@@ -477,28 +477,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D2" t="n">
+        <v>91</v>
+      </c>
+      <c r="E2" t="n">
+        <v>83</v>
+      </c>
+      <c r="F2" t="n">
+        <v>104</v>
+      </c>
+      <c r="G2" t="n">
+        <v>105</v>
+      </c>
+      <c r="H2" t="n">
+        <v>104</v>
+      </c>
+      <c r="I2" t="n">
         <v>103</v>
-      </c>
-      <c r="E2" t="n">
-        <v>91</v>
-      </c>
-      <c r="F2" t="n">
-        <v>83</v>
-      </c>
-      <c r="G2" t="n">
-        <v>104</v>
-      </c>
-      <c r="H2" t="n">
-        <v>105</v>
-      </c>
-      <c r="I2" t="n">
-        <v>104</v>
       </c>
     </row>
     <row r="3">
@@ -508,28 +508,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="C3" t="n">
         <v>428</v>
       </c>
       <c r="D3" t="n">
-        <v>428</v>
+        <v>350</v>
       </c>
       <c r="E3" t="n">
-        <v>350</v>
+        <v>318</v>
       </c>
       <c r="F3" t="n">
-        <v>318</v>
+        <v>426</v>
       </c>
       <c r="G3" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H3" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="I3" t="n">
-        <v>430</v>
+        <v>436</v>
       </c>
     </row>
     <row r="4">
@@ -539,28 +539,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C4" t="n">
         <v>178</v>
       </c>
       <c r="D4" t="n">
+        <v>158</v>
+      </c>
+      <c r="E4" t="n">
+        <v>145</v>
+      </c>
+      <c r="F4" t="n">
+        <v>175</v>
+      </c>
+      <c r="G4" t="n">
+        <v>176</v>
+      </c>
+      <c r="H4" t="n">
         <v>178</v>
       </c>
-      <c r="E4" t="n">
-        <v>158</v>
-      </c>
-      <c r="F4" t="n">
-        <v>145</v>
-      </c>
-      <c r="G4" t="n">
-        <v>175</v>
-      </c>
-      <c r="H4" t="n">
-        <v>176</v>
-      </c>
       <c r="I4" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5">
@@ -570,28 +570,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="C5" t="n">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="D5" t="n">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="E5" t="n">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="F5" t="n">
-        <v>303</v>
+        <v>338</v>
       </c>
       <c r="G5" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H5" t="n">
+        <v>346</v>
+      </c>
+      <c r="I5" t="n">
         <v>339</v>
-      </c>
-      <c r="I5" t="n">
-        <v>346</v>
       </c>
     </row>
     <row r="6">
@@ -632,28 +632,28 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>19</v>
+      </c>
+      <c r="C7" t="n">
         <v>20</v>
       </c>
-      <c r="C7" t="n">
-        <v>19</v>
-      </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H7" t="n">
         <v>21</v>
       </c>
       <c r="I7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -669,13 +669,13 @@
         <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
         <v>14</v>
       </c>
       <c r="F8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G8" t="n">
         <v>15</v>
@@ -694,28 +694,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1977</v>
+        <v>1947</v>
       </c>
       <c r="C9" t="n">
-        <v>1947</v>
+        <v>1963</v>
       </c>
       <c r="D9" t="n">
-        <v>1963</v>
+        <v>1864</v>
       </c>
       <c r="E9" t="n">
-        <v>1864</v>
+        <v>1788</v>
       </c>
       <c r="F9" t="n">
-        <v>1788</v>
+        <v>1950</v>
       </c>
       <c r="G9" t="n">
-        <v>1950</v>
+        <v>1982</v>
       </c>
       <c r="H9" t="n">
-        <v>1982</v>
+        <v>2119</v>
       </c>
       <c r="I9" t="n">
-        <v>2119</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="10">
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>107</v>
+      </c>
+      <c r="C10" t="n">
+        <v>109</v>
+      </c>
+      <c r="D10" t="n">
         <v>104</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
+        <v>96</v>
+      </c>
+      <c r="F10" t="n">
         <v>107</v>
       </c>
-      <c r="D10" t="n">
-        <v>109</v>
-      </c>
-      <c r="E10" t="n">
-        <v>104</v>
-      </c>
-      <c r="F10" t="n">
-        <v>96</v>
-      </c>
       <c r="G10" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H10" t="n">
+        <v>108</v>
+      </c>
+      <c r="I10" t="n">
         <v>105</v>
-      </c>
-      <c r="I10" t="n">
-        <v>108</v>
       </c>
     </row>
     <row r="11">
@@ -756,28 +756,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C11" t="n">
+        <v>231</v>
+      </c>
+      <c r="D11" t="n">
+        <v>205</v>
+      </c>
+      <c r="E11" t="n">
+        <v>195</v>
+      </c>
+      <c r="F11" t="n">
+        <v>225</v>
+      </c>
+      <c r="G11" t="n">
         <v>228</v>
       </c>
-      <c r="D11" t="n">
-        <v>231</v>
-      </c>
-      <c r="E11" t="n">
-        <v>205</v>
-      </c>
-      <c r="F11" t="n">
-        <v>195</v>
-      </c>
-      <c r="G11" t="n">
-        <v>225</v>
-      </c>
       <c r="H11" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I11" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12">
@@ -787,28 +787,28 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>327</v>
+      </c>
+      <c r="C12" t="n">
+        <v>319</v>
+      </c>
+      <c r="D12" t="n">
         <v>326</v>
       </c>
-      <c r="C12" t="n">
+      <c r="E12" t="n">
+        <v>318</v>
+      </c>
+      <c r="F12" t="n">
         <v>327</v>
       </c>
-      <c r="D12" t="n">
-        <v>319</v>
-      </c>
-      <c r="E12" t="n">
-        <v>326</v>
-      </c>
-      <c r="F12" t="n">
-        <v>318</v>
-      </c>
       <c r="G12" t="n">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="H12" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I12" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>

--- a/缓存数据/ds_count_8_Part.xlsx
+++ b/缓存数据/ds_count_8_Part.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -53,18 +53,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -477,28 +477,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="C2" t="n">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="D2" t="n">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="E2" t="n">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="F2" t="n">
+        <v>88</v>
+      </c>
+      <c r="G2" t="n">
+        <v>110</v>
+      </c>
+      <c r="H2" t="n">
+        <v>107</v>
+      </c>
+      <c r="I2" t="n">
         <v>104</v>
-      </c>
-      <c r="G2" t="n">
-        <v>105</v>
-      </c>
-      <c r="H2" t="n">
-        <v>104</v>
-      </c>
-      <c r="I2" t="n">
-        <v>103</v>
       </c>
     </row>
     <row r="3">
@@ -508,28 +508,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="C3" t="n">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="D3" t="n">
-        <v>350</v>
+        <v>429</v>
       </c>
       <c r="E3" t="n">
-        <v>318</v>
+        <v>357</v>
       </c>
       <c r="F3" t="n">
+        <v>315</v>
+      </c>
+      <c r="G3" t="n">
         <v>426</v>
       </c>
-      <c r="G3" t="n">
-        <v>427</v>
-      </c>
       <c r="H3" t="n">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="I3" t="n">
-        <v>436</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4">
@@ -539,28 +539,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C4" t="n">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D4" t="n">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="E4" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="F4" t="n">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="G4" t="n">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="H4" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="I4" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5">
@@ -570,28 +570,28 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>341</v>
+      </c>
+      <c r="C5" t="n">
+        <v>354</v>
+      </c>
+      <c r="D5" t="n">
+        <v>355</v>
+      </c>
+      <c r="E5" t="n">
+        <v>335</v>
+      </c>
+      <c r="F5" t="n">
+        <v>317</v>
+      </c>
+      <c r="G5" t="n">
+        <v>338</v>
+      </c>
+      <c r="H5" t="n">
         <v>336</v>
       </c>
-      <c r="C5" t="n">
-        <v>344</v>
-      </c>
-      <c r="D5" t="n">
-        <v>333</v>
-      </c>
-      <c r="E5" t="n">
-        <v>303</v>
-      </c>
-      <c r="F5" t="n">
-        <v>338</v>
-      </c>
-      <c r="G5" t="n">
-        <v>339</v>
-      </c>
-      <c r="H5" t="n">
-        <v>346</v>
-      </c>
       <c r="I5" t="n">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6">
@@ -632,25 +632,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C7" t="n">
+        <v>26</v>
+      </c>
+      <c r="D7" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16</v>
+      </c>
+      <c r="F7" t="n">
+        <v>13</v>
+      </c>
+      <c r="G7" t="n">
+        <v>22</v>
+      </c>
+      <c r="H7" t="n">
         <v>20</v>
-      </c>
-      <c r="D7" t="n">
-        <v>11</v>
-      </c>
-      <c r="E7" t="n">
-        <v>12</v>
-      </c>
-      <c r="F7" t="n">
-        <v>22</v>
-      </c>
-      <c r="G7" t="n">
-        <v>21</v>
-      </c>
-      <c r="H7" t="n">
-        <v>21</v>
       </c>
       <c r="I7" t="n">
         <v>20</v>
@@ -663,19 +663,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G8" t="n">
         <v>15</v>
@@ -694,28 +694,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1947</v>
+        <v>2010</v>
       </c>
       <c r="C9" t="n">
-        <v>1963</v>
+        <v>2097</v>
       </c>
       <c r="D9" t="n">
-        <v>1864</v>
+        <v>2084</v>
       </c>
       <c r="E9" t="n">
-        <v>1788</v>
+        <v>2132</v>
       </c>
       <c r="F9" t="n">
-        <v>1950</v>
+        <v>2086</v>
       </c>
       <c r="G9" t="n">
-        <v>1982</v>
+        <v>2319</v>
       </c>
       <c r="H9" t="n">
-        <v>2119</v>
+        <v>2233</v>
       </c>
       <c r="I9" t="n">
-        <v>2172</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="10">
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C10" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D10" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E10" t="n">
+        <v>102</v>
+      </c>
+      <c r="F10" t="n">
         <v>96</v>
       </c>
-      <c r="F10" t="n">
-        <v>107</v>
-      </c>
       <c r="G10" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H10" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I10" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11">
@@ -756,28 +756,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C11" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="E11" t="n">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="F11" t="n">
-        <v>225</v>
+        <v>181</v>
       </c>
       <c r="G11" t="n">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="H11" t="n">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="I11" t="n">
-        <v>227</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -787,31 +787,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C12" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D12" t="n">
+        <v>325</v>
+      </c>
+      <c r="E12" t="n">
+        <v>322</v>
+      </c>
+      <c r="F12" t="n">
+        <v>322</v>
+      </c>
+      <c r="G12" t="n">
+        <v>324</v>
+      </c>
+      <c r="H12" t="n">
         <v>326</v>
       </c>
-      <c r="E12" t="n">
-        <v>318</v>
-      </c>
-      <c r="F12" t="n">
-        <v>327</v>
-      </c>
-      <c r="G12" t="n">
+      <c r="I12" t="n">
         <v>321</v>
       </c>
-      <c r="H12" t="n">
-        <v>322</v>
-      </c>
-      <c r="I12" t="n">
-        <v>324</v>
-      </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>